--- a/reports/pdf_change_20260804.xlsx
+++ b/reports/pdf_change_20260804.xlsx
@@ -574,7 +574,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 3,907억   ·   현금 115억(2.9%)      당일 2026-08-04  vs  전영업일 2026-08-03      매수 4종목  /  매도 3종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,001억   ·   현금 116억(2.9%)      당일 2026-08-04  vs  전영업일 2026-08-03      매수 4종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -670,7 +670,7 @@
         <v>54</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>810136620</v>
+        <v>818933760</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         <v>-23</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-643052400</v>
+        <v>-650035200</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>20</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>850920000</v>
+        <v>860160000</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>-13</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-179756850</v>
+        <v>-181708800</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
         <v>17</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>1506837500</v>
+        <v>1523200000</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>-8</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-1030828800</v>
+        <v>-1042022400</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>15</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>822049500</v>
+        <v>830976000</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
     <row r="11" ht="19" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,202억   ·   현금 13억(0.4%)      당일 2026-08-04  vs  전영업일 2026-08-03      매수 0종목  /  매도 0종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,369억   ·   현금 13억(0.4%)      당일 2026-08-04  vs  전영업일 2026-08-03      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B11" s="4" t="n"/>
@@ -847,7 +847,7 @@
     <row r="14" ht="19" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,154억   ·   현금 46억(2.1%)      당일 2026-08-04  vs  전영업일 2026-08-03      매수 4종목  /  매도 4종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,208억   ·   현금 46억(2.1%)      당일 2026-08-04  vs  전영업일 2026-08-03      매수 4종목  /  매도 4종목</t>
         </is>
       </c>
       <c r="B14" s="4" t="n"/>
@@ -943,7 +943,7 @@
         <v>142</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>4085340000</v>
+        <v>4103232000</v>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
@@ -964,7 +964,7 @@
         <v>-41</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-1363526750</v>
+        <v>-1369498400</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>50</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>2996875000</v>
+        <v>3010000000</v>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>-17</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-4331940000</v>
+        <v>-4350912000</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>36</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>1560978000</v>
+        <v>1567814400</v>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         <v>-13</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-2827337500</v>
+        <v>-2839720000</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>19</v>
       </c>
       <c r="C20" s="11" t="n">
-        <v>832960000</v>
+        <v>836608000</v>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>-10</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>-1476175000</v>
+        <v>-1482640000</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
     <row r="22" ht="19" customHeight="1">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 1,919억   ·   현금 23억(1.2%)      당일 2026-08-04  vs  전영업일 2026-08-03      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 1,992억   ·   현금 23억(1.2%)      당일 2026-08-04  vs  전영업일 2026-08-03      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B22" s="4" t="n"/>
@@ -1136,7 +1136,7 @@
     <row r="25" ht="19" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 241억   ·   현금 7억(2.9%)      당일 2026-08-04  vs  전영업일 2026-08-03      매수 0종목  /  매도 0종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 243억   ·   현금 7억(2.9%)      당일 2026-08-04  vs  전영업일 2026-08-03      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B25" s="4" t="n"/>
@@ -1160,7 +1160,7 @@
     <row r="28" ht="19" customHeight="1">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 446억   ·   현금 16억(3.3%)      당일 2026-08-04  vs  전영업일 2026-08-03      매수 2종목  /  매도 1종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 456억   ·   현금 16억(3.3%)      당일 2026-08-04  vs  전영업일 2026-08-03      매수 2종목  /  매도 1종목</t>
         </is>
       </c>
       <c r="B28" s="4" t="n"/>
